--- a/output/2026年4月/党费收缴子表/2026年4月-2026年计算机科学与技术学院研究生第四党支部-党费收缴子表.xlsx
+++ b/output/2026年4月/党费收缴子表/2026年4月-2026年计算机科学与技术学院研究生第四党支部-党费收缴子表.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>姓 名</t>
+          <t>侯俊译</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -628,11 +628,11 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>侯俊译</t>
+          <t>赵俊杰</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
@@ -677,11 +677,11 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>赵俊杰</t>
+          <t>刘鹏媛</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
@@ -726,11 +726,11 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>刘鹏媛</t>
+          <t>张婧玮</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
@@ -775,11 +775,11 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>张婧玮</t>
+          <t>张龙伟</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
@@ -824,11 +824,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>张龙伟</t>
+          <t>吕建宏</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
@@ -873,11 +873,11 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>吕建宏</t>
+          <t>汪贵阳</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
@@ -922,11 +922,11 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>汪贵阳</t>
+          <t>王书娟</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
@@ -971,11 +971,11 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>王书娟</t>
+          <t>卢彦蒿</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
@@ -1020,11 +1020,11 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>卢彦蒿</t>
+          <t>朱自豪</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
@@ -1069,11 +1069,11 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>朱自豪</t>
+          <t>姜瑞清</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -1118,11 +1118,11 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>姜瑞清</t>
+          <t>马嘉宁</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
@@ -1167,11 +1167,11 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>马嘉宁</t>
+          <t>葛慧</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
@@ -1216,11 +1216,11 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>葛慧</t>
+          <t>闫大利</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
@@ -1265,11 +1265,11 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>闫大利</t>
+          <t>李梦洁</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
@@ -1314,11 +1314,11 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>李梦洁</t>
+          <t>李雨轩</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
@@ -1363,11 +1363,11 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>李雨轩</t>
+          <t>尤镇峰</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
@@ -1412,11 +1412,11 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>尤镇峰</t>
+          <t>李思颖</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
@@ -1461,11 +1461,11 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>李思颖</t>
+          <t>魏美玲</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
@@ -1510,11 +1510,11 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>魏美玲</t>
+          <t>王乐</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
@@ -1559,11 +1559,11 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>王乐</t>
+          <t>彭浩</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
@@ -1608,11 +1608,11 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>彭浩</t>
+          <t>葛佳旋</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
@@ -1657,11 +1657,11 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>葛佳旋</t>
+          <t>陈永增</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
@@ -1706,11 +1706,11 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>陈永增</t>
+          <t>田伟烨</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
@@ -1755,11 +1755,11 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>田伟烨</t>
+          <t>张若雯</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
@@ -1804,11 +1804,11 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>张若雯</t>
+          <t>汤同舟</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
@@ -1853,11 +1853,11 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>汤同舟</t>
+          <t>王煜青</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
@@ -1902,11 +1902,11 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>王煜青</t>
+          <t>刘洋</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
@@ -1950,83 +1950,34 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="8" t="n"/>
-      <c r="L33" s="8" t="n"/>
-      <c r="M33" s="8" t="n"/>
-      <c r="N33" s="8" t="n"/>
-      <c r="O33" s="3" t="n">
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="8" t="n"/>
+      <c r="M32" s="8" t="n"/>
+      <c r="N32" s="8" t="n"/>
+      <c r="O32" s="3" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A32:N32"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="G2:N2"/>
-    <mergeCell ref="A33:N33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
